--- a/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,58</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>32,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,09</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,58</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,14</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>25,93</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,06; 18,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,19; 35,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,59; 37,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,29; 11,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,13; 14,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,12; 18,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,06; 15,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,7; 26,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,71; 30,31</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,15; 51,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,17; 102,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,51; 104,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,33; 15,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,5; 18,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,58; 24,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,72; 29,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,81; 50,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,8; 57,53</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,08</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>22,29</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,48</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,56</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>15,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,43; 14,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,36; 25,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,35; 28,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,66; 9,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,08; 14,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,81; 14,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,25; 9,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,86; 18,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,2; 19,74</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,69; 32,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,32; 58,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,18; 68,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,76; 12,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,85; 18,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,67; 18,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,83; 14,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,82; 28,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,08; 32,09</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,23</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>21,36</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,71</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,28</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,51; 19,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,67; 27,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,18; 34,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,76; 4,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,6; 10,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,87; 9,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,54; 16,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,06; 22,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,36; 28,1</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,07; 61,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,46; 91,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-52,28; 104,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,81; 5,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,88; 12,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,23; 11,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,96; 38,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,4; 51,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-47,1; 60,9</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,33</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>20,16</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,22</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>16,16</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,09; 14,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,78; 24,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,99; 38,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,79; 6,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,57; 7,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,56; 13,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,98; 12,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,17; 19,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,19; 35,44</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>102,81%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,15; 46,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,92; 80,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,61; 124,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,94; 7,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,65; 8,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,52; 16,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,07; 24,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,33; 37,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,38; 68,32</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,29</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>26,34</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-3,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,55; 11,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,49; 16,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,99; 33,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,41; -0,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,76; 3,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,25; 6,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,36; 2,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,83; 4,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,14; 17,4</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,07%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,13; 37,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,35; 51,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,36; 104,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,01; -0,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,96; 4,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,36; 7,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,46; 3,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,85; 7,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,68; 25,87</t>
         </is>
       </c>
     </row>
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,99</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,23</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>35,56</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-5,85</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-4,39</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,3; 8,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,39; 20,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,9; 46,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,3; -2,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,21; 2,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,57; 3,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,12; -1,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,31; 4,53</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,61; 9,57</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>112,3%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>301,83%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-7,27%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-6,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,91; 94,93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,54; 222,62</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>160,56; 472,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,35; -2,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,2; 3,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,33; 4,99</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,8; -1,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,42; 6,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,97; 14,43</t>
         </is>
       </c>
     </row>
@@ -1920,47 +1920,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,56</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,95</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>26,96</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,41</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,09</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,23</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,06; 11,98</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,32; 21,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,45; 32,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,37; 1,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,68; 4,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,66; 9,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,69; 6,02</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,45; 12,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,56; 20,85</t>
         </is>
       </c>
     </row>
@@ -2026,47 +2026,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,65%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,81; 36,4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,47; 65,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,44; 96,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,78; 1,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,0; 5,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,65; 11,26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,45; 10,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,54; 21,69</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,84; 35,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32,02</t>
+          <t>31,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25,93</t>
+          <t>25,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 18,66</t>
+          <t>5,13; 19,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,19; 35,09</t>
+          <t>21,88; 35,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,59; 37,8</t>
+          <t>25,64; 37,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 11,5</t>
+          <t>-0,76; 12,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 14,25</t>
+          <t>1,39; 13,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 18,05</t>
+          <t>7,49; 18,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 15,71</t>
+          <t>4,93; 15,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,7; 26,44</t>
+          <t>16,48; 26,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,71; 30,31</t>
+          <t>21,38; 30,42</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 51,92</t>
+          <t>12,16; 54,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,17; 102,44</t>
+          <t>49,72; 99,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,51; 104,53</t>
+          <t>58,96; 105,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 15,14</t>
+          <t>-1,0; 15,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 18,63</t>
+          <t>1,63; 18,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 24,17</t>
+          <t>9,14; 24,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 29,95</t>
+          <t>8,57; 29,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,81; 50,5</t>
+          <t>28,25; 51,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,8; 57,53</t>
+          <t>36,82; 57,8</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,29</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>10,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>15,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 14,0</t>
+          <t>-0,51; 14,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 25,35</t>
+          <t>10,87; 26,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,35; 28,98</t>
+          <t>14,83; 29,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 9,9</t>
+          <t>-0,46; 10,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 14,64</t>
+          <t>5,16; 14,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 14,77</t>
+          <t>5,91; 14,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 9,29</t>
+          <t>-1,03; 8,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 18,27</t>
+          <t>8,81; 18,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 19,74</t>
+          <t>10,94; 19,85</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 32,27</t>
+          <t>-1,03; 34,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,32; 58,57</t>
+          <t>21,48; 60,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,18; 68,05</t>
+          <t>28,9; 68,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 12,27</t>
+          <t>-0,38; 13,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 18,25</t>
+          <t>5,95; 17,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 18,21</t>
+          <t>6,85; 18,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 14,97</t>
+          <t>-1,44; 14,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 28,91</t>
+          <t>12,85; 28,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,08; 32,09</t>
+          <t>16,36; 32,03</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>30,83</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>25,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 19,19</t>
+          <t>7,49; 18,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 27,76</t>
+          <t>14,99; 27,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 34,18</t>
+          <t>24,88; 36,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 4,54</t>
+          <t>-9,03; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 10,29</t>
+          <t>-3,87; 10,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 9,76</t>
+          <t>-4,57; 9,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 16,93</t>
+          <t>6,12; 16,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 22,72</t>
+          <t>11,98; 22,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 28,1</t>
+          <t>19,81; 30,64</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,07; 61,14</t>
+          <t>20,46; 61,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,46; 91,47</t>
+          <t>40,29; 86,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 104,57</t>
+          <t>65,82; 119,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 5,39</t>
+          <t>-9,81; 6,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 12,5</t>
+          <t>-4,17; 12,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 11,7</t>
+          <t>-4,91; 11,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,96; 38,2</t>
+          <t>12,37; 37,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,4; 51,93</t>
+          <t>24,09; 50,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 60,9</t>
+          <t>40,48; 69,69</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34,22</t>
+          <t>33,48</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,6</t>
+          <t>8,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28,64</t>
+          <t>26,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 14,31</t>
+          <t>5,73; 14,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,78; 24,39</t>
+          <t>15,85; 24,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,99; 38,45</t>
+          <t>29,38; 37,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,03</t>
+          <t>-0,69; 6,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,05</t>
+          <t>0,89; 7,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 13,57</t>
+          <t>5,62; 11,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 12,18</t>
+          <t>5,74; 12,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,17; 19,15</t>
+          <t>13,05; 19,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,19; 35,44</t>
+          <t>23,19; 29,22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102,81%</t>
+          <t>100,58%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,15; 46,49</t>
+          <t>16,53; 46,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,92; 80,75</t>
+          <t>44,49; 76,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,61; 124,4</t>
+          <t>83,75; 120,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 7,13</t>
+          <t>-0,78; 7,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 8,38</t>
+          <t>1,0; 8,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 16,27</t>
+          <t>6,38; 14,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,07; 24,07</t>
+          <t>10,67; 24,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,33; 37,72</t>
+          <t>24,0; 38,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46,38; 68,32</t>
+          <t>42,76; 57,47</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26,34</t>
+          <t>26,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,17</t>
+          <t>11,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 11,36</t>
+          <t>-2,2; 12,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,49; 16,14</t>
+          <t>4,27; 17,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,99; 33,09</t>
+          <t>19,12; 33,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -0,43</t>
+          <t>-7,18; -0,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,92</t>
+          <t>-2,65; 3,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,79</t>
+          <t>0,92; 6,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,43</t>
+          <t>-5,1; 2,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 4,85</t>
+          <t>-3,09; 4,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,14; 17,4</t>
+          <t>7,35; 15,09</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 37,94</t>
+          <t>-5,59; 37,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8,35; 51,15</t>
+          <t>10,61; 55,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47,36; 104,86</t>
+          <t>47,17; 107,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -0,5</t>
+          <t>-7,89; -0,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 4,45</t>
+          <t>-2,9; 4,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,68</t>
+          <t>0,99; 7,4</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,57</t>
+          <t>-7,15; 4,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 7,21</t>
+          <t>-4,22; 6,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,68; 25,87</t>
+          <t>10,1; 22,32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35,56</t>
+          <t>32,75</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>5,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,16</t>
+          <t>-3,63; 8,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,39; 20,28</t>
+          <t>6,82; 19,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23,9; 46,91</t>
+          <t>22,7; 43,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -2,35</t>
+          <t>-9,01; -2,66</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 2,44</t>
+          <t>-4,11; 2,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,95</t>
+          <t>-3,49; 4,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,12; -1,02</t>
+          <t>-8,06; -1,19</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,53</t>
+          <t>-2,5; 4,48</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,61; 9,57</t>
+          <t>0,89; 9,8</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>301,83%</t>
+          <t>277,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 94,93</t>
+          <t>-26,56; 88,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>41,54; 222,62</t>
+          <t>42,0; 218,26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>160,56; 472,97</t>
+          <t>166,92; 481,29</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -2,93</t>
+          <t>-11,05; -3,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 3,1</t>
+          <t>-5,02; 3,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 4,99</t>
+          <t>-4,27; 5,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -1,54</t>
+          <t>-11,75; -1,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 6,84</t>
+          <t>-3,6; 6,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,97; 14,43</t>
+          <t>1,37; 14,86</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26,96</t>
+          <t>31,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,41</t>
+          <t>6,7</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,23</t>
+          <t>18,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,98</t>
+          <t>7,12; 11,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16,32; 21,38</t>
+          <t>16,5; 21,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,45; 32,73</t>
+          <t>28,84; 33,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,18</t>
+          <t>-2,39; 1,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,97</t>
+          <t>1,62; 4,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,43</t>
+          <t>5,27; 8,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,02</t>
+          <t>2,77; 6,12</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,45; 12,75</t>
+          <t>9,52; 12,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,56; 20,85</t>
+          <t>17,2; 20,48</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>19,81; 36,4</t>
+          <t>20,05; 36,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>46,47; 65,49</t>
+          <t>45,79; 64,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24,44; 96,67</t>
+          <t>80,91; 103,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,42</t>
+          <t>-2,81; 1,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,99</t>
+          <t>1,89; 6,01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,65; 11,26</t>
+          <t>6,08; 9,97</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,45; 10,3</t>
+          <t>4,59; 10,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15,54; 21,69</t>
+          <t>15,7; 21,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12,84; 35,29</t>
+          <t>28,58; 34,92</t>
         </is>
       </c>
     </row>
